--- a/KatalonData/EmailTextToPay/BillFileLookUp_Upgrade.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp_Upgrade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F373ED6-41B5-4C64-A01D-07C1D9C018CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE0C132-F71E-462D-B9A9-D5C229D3B52D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="158">
   <si>
     <t>Result</t>
   </si>
@@ -287,99 +287,12 @@
     <t>45332116803cA</t>
   </si>
   <si>
-    <t>Thu Jul 09 10:52:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:52:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:53:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:54:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:55:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:55:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:56:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:57:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:57:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:58:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:59:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 10:59:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 11:00:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 11:00:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 11:01:36 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 11:02:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 11:02:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 11:03:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 11:04:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 11:05:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 11:05:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 11:06:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 11:07:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 11:07:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 09 11:08:19 IST 2026</t>
-  </si>
-  <si>
     <t>Mon Jul 13 14:09:52 IST 2026</t>
   </si>
   <si>
-    <t>Mon Jul 13 14:12:24 IST 2026</t>
-  </si>
-  <si>
     <t>Mon Jul 13 14:13:11 IST 2026</t>
   </si>
   <si>
-    <t>Mon Jul 13 14:13:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 14:15:10 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 14:16:42 IST 2026</t>
-  </si>
-  <si>
     <t>Mon Jul 13 14:18:06 IST 2026</t>
   </si>
   <si>
@@ -398,15 +311,6 @@
     <t>Mon Jul 13 14:22:13 IST 2026</t>
   </si>
   <si>
-    <t>Mon Jul 13 14:22:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 14:23:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 14:24:39 IST 2026</t>
-  </si>
-  <si>
     <t>Mon Jul 13 14:25:39 IST 2026</t>
   </si>
   <si>
@@ -416,30 +320,6 @@
     <t>Mon Jul 13 14:27:27 IST 2026</t>
   </si>
   <si>
-    <t>Mon Jul 13 14:28:10 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 14:29:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 14:30:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 14:30:57 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 14:31:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 14:32:31 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 14:33:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:06:28 IST 2026</t>
-  </si>
-  <si>
     <t>Mon Jul 13 15:15:15 IST 2026</t>
   </si>
   <si>
@@ -479,15 +359,6 @@
     <t>Mon Jul 13 15:25:27 IST 2026</t>
   </si>
   <si>
-    <t>Mon Jul 13 15:35:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:37:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Jul 13 15:38:00 IST 2026</t>
-  </si>
-  <si>
     <t>Mon Jul 13 15:43:47 IST 2026</t>
   </si>
   <si>
@@ -561,6 +432,90 @@
   </si>
   <si>
     <t>Mon Jul 13 16:08:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 21:52:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 21:52:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:05:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:05:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:06:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:07:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:08:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:08:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:09:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:10:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:10:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:11:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:12:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:12:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:13:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:14:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:14:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:15:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:16:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:17:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:17:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:18:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:19:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:19:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:20:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:21:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:21:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 23:22:23 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -593,12 +548,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -628,7 +589,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -653,6 +614,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1045,11 +1009,14 @@
         <v>70</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>10</v>
       </c>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="E2" s="4" t="s">
         <v>71</v>
       </c>
@@ -1058,15 +1025,18 @@
       </c>
     </row>
     <row r="3" spans="1:11" ht="13" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>75</v>
+      <c r="A3" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>11</v>
       </c>
+      <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="E3" s="4" t="s">
         <v>71</v>
       </c>
@@ -1075,15 +1045,18 @@
       </c>
     </row>
     <row r="4" spans="1:11" ht="13" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>75</v>
+      <c r="A4" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>12</v>
       </c>
+      <c r="D4" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="E4" s="4" t="s">
         <v>71</v>
       </c>
@@ -1092,15 +1065,18 @@
       </c>
     </row>
     <row r="5" spans="1:11" ht="13" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>75</v>
+      <c r="A5" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>13</v>
       </c>
+      <c r="D5" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="E5" s="4" t="s">
         <v>71</v>
       </c>
@@ -1113,7 +1089,7 @@
         <v>70</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>55</v>
@@ -1133,7 +1109,7 @@
         <v>70</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>28</v>
@@ -1153,7 +1129,7 @@
         <v>70</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>29</v>
@@ -1173,11 +1149,14 @@
         <v>70</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
+      <c r="D9" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="E9" s="4" t="s">
         <v>71</v>
       </c>
@@ -1205,11 +1184,14 @@
         <v>70</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>15</v>
       </c>
+      <c r="D10" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="E10" s="4" t="s">
         <v>71</v>
       </c>
@@ -1221,15 +1203,18 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="13" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>75</v>
+      <c r="A11" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>14</v>
       </c>
+      <c r="D11" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="E11" s="4" t="s">
         <v>71</v>
       </c>
@@ -1241,15 +1226,18 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="13" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>75</v>
+      <c r="A12" s="9" t="s">
+        <v>70</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>38</v>
       </c>
+      <c r="D12" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="E12" s="4" t="s">
         <v>71</v>
       </c>
@@ -1265,11 +1253,14 @@
         <v>70</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>16</v>
       </c>
+      <c r="D13" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="E13" s="4" t="s">
         <v>71</v>
       </c>
@@ -1285,11 +1276,14 @@
         <v>70</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>17</v>
       </c>
+      <c r="D14" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="E14" s="4" t="s">
         <v>71</v>
       </c>
@@ -1305,7 +1299,7 @@
         <v>70</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>30</v>
@@ -1328,7 +1322,7 @@
         <v>70</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>31</v>
@@ -1351,7 +1345,7 @@
         <v>70</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>56</v>
@@ -1374,11 +1368,14 @@
         <v>70</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>32</v>
       </c>
+      <c r="D18" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="E18" s="4" t="s">
         <v>71</v>
       </c>
@@ -1394,11 +1391,14 @@
         <v>70</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>33</v>
       </c>
+      <c r="D19" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="E19" s="4" t="s">
         <v>71</v>
       </c>
@@ -1414,11 +1414,14 @@
         <v>70</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>57</v>
       </c>
+      <c r="D20" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="E20" s="4" t="s">
         <v>71</v>
       </c>
@@ -1434,7 +1437,7 @@
         <v>70</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>54</v>
@@ -1460,7 +1463,7 @@
         <v>70</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>34</v>
@@ -1483,7 +1486,7 @@
         <v>70</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>35</v>
@@ -1506,7 +1509,7 @@
         <v>70</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>58</v>
@@ -1529,7 +1532,7 @@
         <v>70</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>36</v>
@@ -1552,7 +1555,7 @@
         <v>70</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>37</v>
@@ -1575,7 +1578,7 @@
         <v>70</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>59</v>
@@ -1659,7 +1662,7 @@
         <v>70</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>76</v>
@@ -1685,7 +1688,7 @@
         <v>70</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>149</v>
+        <v>106</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>77</v>
@@ -1705,7 +1708,7 @@
         <v>70</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>150</v>
+        <v>107</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>78</v>
@@ -1789,7 +1792,7 @@
         <v>70</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>151</v>
+        <v>108</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>20</v>
@@ -1812,7 +1815,7 @@
         <v>70</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>21</v>
@@ -1835,7 +1838,7 @@
         <v>70</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>153</v>
+        <v>110</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>22</v>
@@ -1858,7 +1861,7 @@
         <v>70</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>154</v>
+        <v>111</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>23</v>
@@ -1881,7 +1884,7 @@
         <v>70</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>155</v>
+        <v>112</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>39</v>
@@ -1904,7 +1907,7 @@
         <v>70</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>156</v>
+        <v>113</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>40</v>
@@ -1927,7 +1930,7 @@
         <v>70</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>157</v>
+        <v>114</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>41</v>
@@ -1953,7 +1956,7 @@
         <v>70</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>158</v>
+        <v>115</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>42</v>
@@ -1979,7 +1982,7 @@
         <v>70</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>44</v>
@@ -2005,7 +2008,7 @@
         <v>70</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>43</v>
@@ -2031,7 +2034,7 @@
         <v>70</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>161</v>
+        <v>118</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>49</v>
@@ -2057,7 +2060,7 @@
         <v>70</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>50</v>
@@ -2083,7 +2086,7 @@
         <v>70</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>163</v>
+        <v>120</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>51</v>
@@ -2109,7 +2112,7 @@
         <v>70</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>164</v>
+        <v>121</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>45</v>
@@ -2135,7 +2138,7 @@
         <v>70</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>165</v>
+        <v>122</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>46</v>
@@ -2161,7 +2164,7 @@
         <v>70</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>166</v>
+        <v>123</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>47</v>
@@ -2187,7 +2190,7 @@
         <v>70</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>167</v>
+        <v>124</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>48</v>
@@ -2213,7 +2216,7 @@
         <v>70</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>168</v>
+        <v>125</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>64</v>
@@ -2236,7 +2239,7 @@
         <v>70</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>169</v>
+        <v>126</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>66</v>
@@ -2262,7 +2265,7 @@
         <v>70</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>170</v>
+        <v>127</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>67</v>
@@ -2288,7 +2291,7 @@
         <v>70</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>68</v>
@@ -2314,7 +2317,7 @@
         <v>70</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>172</v>
+        <v>129</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>69</v>
